--- a/output/第10期計画_将来推計_需要3シナリオの感度表.xlsx
+++ b/output/第10期計画_将来推計_需要3シナリオの感度表.xlsx
@@ -3913,7 +3913,7 @@
     <row r="13" ht="104" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>注1）認知症対応型共同生活介護の区域内定員99人は、グループホームくるみの郷1事業所を含まない。同事業所は介護サービス情報公表システムに掲載がなく定員を確認できていないため、居住系の定員は過小である（資料提供依頼No.18、点検事項No.35）。注2）施設・居住系の見込量は定員により制約される。高位シナリオが定員を超える場合は、整備するか、区域外の施設の利用を見込むかの判断を要する。注3）特定施設は定員156人に対し入居者154人（98.7％）でほぼ満室である。居住系の見込量の上振れを区域内で受けられる余地は小さい。</t>
+          <t>注1）認知症対応型共同生活介護の区域内定員99人は、グループホームくるみの郷1事業所を含まない。同事業所は介護サービス情報公表システムに掲載がなく定員を確認できていないため、居住系の定員は過小である（資料提供依頼No.18、点検事項No.35）。注2）施設・居住系の見込量は定員により制約される。高位シナリオが定員を超える場合は、整備するか、区域外の施設の利用を見込むかの判断を要する。注3）特定施設は区域内3施設とも入居率が高い（回答2施設98.3％・公表データによる1施設97.0％。時点が異なるため合計の98.7％は参考値）。居住系の見込量の上振れを区域内で受けられる余地は小さい。</t>
         </is>
       </c>
     </row>
